--- a/artfynd/A 54055-2022 artfynd.xlsx
+++ b/artfynd/A 54055-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 54055-2022 artfynd.xlsx
+++ b/artfynd/A 54055-2022 artfynd.xlsx
@@ -675,39 +675,30 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104074255</v>
+        <v>104074253</v>
       </c>
       <c r="B2" t="n">
-        <v>85253</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87403</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1988</v>
+        <v>433</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Fr.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -715,10 +706,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>738294.8794794149</v>
+        <v>738295</v>
       </c>
       <c r="R2" t="n">
-        <v>6416061.339219336</v>
+        <v>6416061</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +739,9 @@
           <t>2022-10-12</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,37 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104074253</v>
+        <v>104074249</v>
       </c>
       <c r="B3" t="n">
-        <v>85148</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87322</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>433</v>
+        <v>1988</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>M. M. Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>738294.8794794149</v>
+        <v>738313</v>
       </c>
       <c r="R3" t="n">
-        <v>6416061.339219336</v>
+        <v>6416075</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,19 +845,9 @@
           <t>2022-10-12</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,15 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104074261</v>
+        <v>104074255</v>
       </c>
       <c r="B4" t="n">
-        <v>85278</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87322</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,21 +894,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6003295</v>
+        <v>1988</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -957,10 +918,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>738336.087958583</v>
+        <v>738295</v>
       </c>
       <c r="R4" t="n">
-        <v>6415907.885099753</v>
+        <v>6416061</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,19 +951,9 @@
           <t>2022-10-12</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,37 +989,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104074259</v>
+        <v>104074254</v>
       </c>
       <c r="B5" t="n">
-        <v>85278</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87146</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1078,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>738339.8854646595</v>
+        <v>738295</v>
       </c>
       <c r="R5" t="n">
-        <v>6415970.044747196</v>
+        <v>6416061</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,19 +1057,9 @@
           <t>2022-10-12</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,15 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104074258</v>
+        <v>104074248</v>
       </c>
       <c r="B6" t="n">
-        <v>86196</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89143</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,10 +1130,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>738349.4597244652</v>
+        <v>738313</v>
       </c>
       <c r="R6" t="n">
-        <v>6416015.99554424</v>
+        <v>6416075</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1232,19 +1163,9 @@
           <t>2022-10-12</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,15 +1201,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104074248</v>
+        <v>104074258</v>
       </c>
       <c r="B7" t="n">
-        <v>86196</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89143</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,10 +1236,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>738312.8091697432</v>
+        <v>738349</v>
       </c>
       <c r="R7" t="n">
-        <v>6416074.683574222</v>
+        <v>6416016</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1353,19 +1269,9 @@
           <t>2022-10-12</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1401,37 +1307,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104074254</v>
+        <v>104074259</v>
       </c>
       <c r="B8" t="n">
-        <v>85077</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87346</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1441,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>738294.8794794149</v>
+        <v>738340</v>
       </c>
       <c r="R8" t="n">
-        <v>6416061.339219336</v>
+        <v>6415970</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1474,19 +1375,9 @@
           <t>2022-10-12</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1522,37 +1413,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104074249</v>
+        <v>104074261</v>
       </c>
       <c r="B9" t="n">
-        <v>85253</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87346</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1988</v>
+        <v>6003295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1562,10 +1448,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>738312.8091697432</v>
+        <v>738336</v>
       </c>
       <c r="R9" t="n">
-        <v>6416074.683574222</v>
+        <v>6415908</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1595,19 +1481,9 @@
           <t>2022-10-12</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 54055-2022 artfynd.xlsx
+++ b/artfynd/A 54055-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104074253</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104074249</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -986,6 +1001,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104074255</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,6 +1112,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104074254</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1198,6 +1223,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104074248</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1304,6 +1334,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104074258</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1410,6 +1445,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104074259</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1516,8 +1556,23 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104074261</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>